--- a/stories/arbres/TREE-VIV-024.xlsx
+++ b/stories/arbres/TREE-VIV-024.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurore est à la ferme avec maman. Un coq chante. Une poule picore. Un poussin suit. Maman dit : trois noms de la famille. Coq, poule, poussin. Aurore répète.</t>
+          <t>Aurore est à la ferme avec maman. Un coq chante. Une poule picore. Un poussin suit. Trois noms de la famille. Coq, poule, poussin. Aurore répète.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore est à la ferme avec maman. Un coq chante. Une poule picore. Un poussin suit.
+maman|Trois noms de la famille. Coq, poule, poussin.
+narrateur|Aurore répète.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poulailler, le pré, ou la niche.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Au poulailler, Aurore dit les trois noms : coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Au poulailler, le petit c'est qui ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore a dit les trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le coq, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le coq, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le coq, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms. Cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le cheval, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le cheval, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le cheval, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms. Chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le chien, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le chien, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le chien, à le poulailler. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Au pré, Aurore dit les trois noms : cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Au pré, le petit c'est qui ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Trois noms. Mâle, femelle, petit.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le coq, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le coq, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le coq, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms. Cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le cheval, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le cheval, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le cheval, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms. Chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le chien, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le chien, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le chien, à le pré. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11262,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|À la niche, Aurore dit les trois noms : chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11443,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|À la niche, le petit c'est qui ?</t>
         </is>
       </c>
     </row>
@@ -11293,6 +11612,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore répète la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11479,6 +11803,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11641,6 +11970,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms de la famille. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11827,6 +12161,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11989,6 +12328,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le coq, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12151,6 +12495,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12313,6 +12662,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le coq, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12475,6 +12829,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12637,6 +12996,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le coq, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12799,6 +13163,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12961,6 +13330,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms. Cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13147,6 +13521,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13309,6 +13688,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le cheval, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13471,6 +13855,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13633,6 +14022,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le cheval, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13795,6 +14189,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13957,6 +14356,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le cheval, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14119,6 +14523,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14281,6 +14690,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore dit les trois noms. Chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14467,6 +14881,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14629,6 +15048,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poussin près de le chien, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14791,6 +15215,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14953,6 +15382,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le poulain près de le chien, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15115,6 +15549,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15277,6 +15716,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Aurore montre le chiot près de le chien, à la niche. Trois noms de la famille.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15439,6 +15883,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15457,7 +15906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15474,6 +15923,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-024.xlsx
+++ b/stories/arbres/TREE-VIV-024.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Aurore répète.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le poulailler, le pré, ou la niche.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Au poulailler, Aurore dit les trois noms : coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Au poulailler, le petit c'est qui ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Aurore a dit les trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,11 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2395,6 +2410,7 @@
           <t>narrateur|Aurore dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2602,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2770,7 @@
           <t>narrateur|Aurore montre le poussin près de le coq, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3106,7 @@
           <t>narrateur|Aurore montre le poulain près de le coq, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3442,7 @@
           <t>narrateur|Aurore montre le chiot près de le coq, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3778,7 @@
           <t>narrateur|Aurore dit les trois noms. Cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3970,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4138,7 @@
           <t>narrateur|Aurore montre le poussin près de le cheval, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4474,7 @@
           <t>narrateur|Aurore montre le poulain près de le cheval, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4810,7 @@
           <t>narrateur|Aurore montre le chiot près de le cheval, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5146,11 @@
           <t>narrateur|Aurore dit les trois noms. Chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5342,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5510,11 @@
           <t>narrateur|Aurore montre le poussin près de le chien, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5850,11 @@
           <t>narrateur|Aurore montre le poulain près de le chien, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6190,11 @@
           <t>narrateur|Aurore montre le chiot près de le chien, à le poulailler. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6530,7 @@
           <t>narrateur|Au pré, Aurore dit les trois noms : cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6714,7 @@
           <t>narrateur|Au pré, le petit c'est qui ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6886,7 @@
           <t>narrateur|Oui. Trois noms. Mâle, femelle, petit.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7018,6 +7076,11 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7187,6 +7250,7 @@
           <t>narrateur|Aurore dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7442,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7610,7 @@
           <t>narrateur|Aurore montre le poussin près de le coq, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7946,7 @@
           <t>narrateur|Aurore montre le poulain près de le coq, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8282,7 @@
           <t>narrateur|Aurore montre le chiot près de le coq, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8618,7 @@
           <t>narrateur|Aurore dit les trois noms. Cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8810,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8978,7 @@
           <t>narrateur|Aurore montre le poussin près de le cheval, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9146,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9314,7 @@
           <t>narrateur|Aurore montre le poulain près de le cheval, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9482,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9650,7 @@
           <t>narrateur|Aurore montre le chiot près de le cheval, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9818,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9986,11 @@
           <t>narrateur|Aurore dit les trois noms. Chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10182,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10350,11 @@
           <t>narrateur|Aurore montre le poussin près de le chien, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10690,11 @@
           <t>narrateur|Aurore montre le poulain près de le chien, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +11030,11 @@
           <t>narrateur|Aurore montre le chiot près de le chien, à le pré. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11202,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11267,6 +11370,11 @@
           <t>narrateur|À la niche, Aurore dit les trois noms : chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11450,6 +11558,7 @@
           <t>narrateur|À la niche, le petit c'est qui ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11617,6 +11726,7 @@
           <t>narrateur|Aurore répète la famille.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11806,6 +11916,11 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le coq, le cheval, ou le chien.</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -11975,6 +12090,7 @@
           <t>narrateur|Aurore dit les trois noms de la famille. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12166,6 +12282,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12333,6 +12450,7 @@
           <t>narrateur|Aurore montre le poussin près de le coq, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12500,6 +12618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12667,6 +12786,7 @@
           <t>narrateur|Aurore montre le poulain près de le coq, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12834,6 +12954,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13001,6 +13122,7 @@
           <t>narrateur|Aurore montre le chiot près de le coq, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13168,6 +13290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13335,6 +13458,7 @@
           <t>narrateur|Aurore dit les trois noms. Cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13526,6 +13650,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13693,6 +13818,7 @@
           <t>narrateur|Aurore montre le poussin près de le cheval, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13860,6 +13986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14027,6 +14154,7 @@
           <t>narrateur|Aurore montre le poulain près de le cheval, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14194,6 +14322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14361,6 +14490,7 @@
           <t>narrateur|Aurore montre le chiot près de le cheval, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14528,6 +14658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14695,6 +14826,11 @@
           <t>narrateur|Aurore dit les trois noms. Chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14886,6 +15022,7 @@
           <t>narrateur|On peut prendre le poussin, le poulain, ou le chiot.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15053,6 +15190,11 @@
           <t>narrateur|Aurore montre le poussin près de le chien, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15220,6 +15362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15387,6 +15530,11 @@
           <t>narrateur|Aurore montre le poulain près de le chien, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15554,6 +15702,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15721,6 +15870,11 @@
           <t>narrateur|Aurore montre le chiot près de le chien, à la niche. Trois noms de la famille.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15888,6 +16042,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15906,7 +16061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15930,6 +16085,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15944,7 +16113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16131,6 +16300,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
